--- a/oats/testcases/case24_ieee_rts.xlsx
+++ b/oats/testcases/case24_ieee_rts.xlsx
@@ -8506,4 +8506,265 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100206C8747921DEB47908282AF5FC82B21" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a83cb61413023faca73dea3686c4c1f2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6dce361f-7b53-4909-8b0d-30e42626cdc9" xmlns:ns3="3610aed6-0335-46d2-b190-87c476b048cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e915d63bb79862bf9918b8de94dc5ea2" ns2:_="" ns3:_="">
+    <xsd:import namespace="6dce361f-7b53-4909-8b0d-30e42626cdc9"/>
+    <xsd:import namespace="3610aed6-0335-46d2-b190-87c476b048cc"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6dce361f-7b53-4909-8b0d-30e42626cdc9" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="15" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="87865813-b24e-4515-aac3-72cd3b0aa1df" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="19" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="20" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3610aed6-0335-46d2-b190-87c476b048cc" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="16" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{afb7282a-b4e1-44aa-9a85-3d59d972ca27}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3610aed6-0335-46d2-b190-87c476b048cc">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dce361f-7b53-4909-8b0d-30e42626cdc9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3610aed6-0335-46d2-b190-87c476b048cc" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10F1EBA0-29BF-48E2-A80A-4674517565D0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC2D0AC-7F98-441E-A612-742C1D303422}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5205A12-A3DB-4C53-8C3E-4762946BF8BA}"/>
 </file>
--- a/oats/testcases/case24_ieee_rts.xlsx
+++ b/oats/testcases/case24_ieee_rts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/waqquasbukhsh/GitHub/oats/oats/testcases/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/waqquasbukhsh/GitHub/oats/OATS-testcases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6303D4-ECC5-2848-96C6-A64D1DDF365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD5CC85-B449-EB48-8CDB-29C654BE2AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25240" windowHeight="16080" tabRatio="500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21440" windowHeight="12260" tabRatio="500" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="bus" sheetId="1" r:id="rId1"/>
@@ -24,9 +24,8 @@
     <sheet name="baseMVA" sheetId="9" r:id="rId9"/>
     <sheet name="timeseries" sheetId="10" r:id="rId10"/>
     <sheet name="zone" sheetId="11" r:id="rId11"/>
-    <sheet name="storage" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="351">
   <si>
     <t>name</t>
   </si>
@@ -1097,40 +1096,13 @@
   </si>
   <si>
     <t>reserve(MW)</t>
-  </si>
-  <si>
-    <t>Minoperatingcapacity(MW)</t>
-  </si>
-  <si>
-    <t>capacity(MW)</t>
-  </si>
-  <si>
-    <t>chargingrate(MW/hr)</t>
-  </si>
-  <si>
-    <t>dischargingrate(MW/hr)</t>
-  </si>
-  <si>
-    <t>ChargingEfficieny(%)</t>
-  </si>
-  <si>
-    <t>DischargingEfficieny(%)</t>
-  </si>
-  <si>
-    <t>FinalStoredPower(MW)</t>
-  </si>
-  <si>
-    <t>PSH</t>
-  </si>
-  <si>
-    <t>InitialStoredPower(MW)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1145,19 +1117,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1360,8 +1319,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1397,11 +1359,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1725,802 +1682,802 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="4">
         <v>1.05</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
-      <c r="D3" s="6">
+      <c r="C3" s="7">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="7">
         <v>1.05</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="F3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>1</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="7">
         <v>1</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="7">
         <v>1.05</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="F4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>1</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="7">
         <v>1.05</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>1</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <v>1</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>1.05</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>1.05</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="6">
-        <v>2</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>1.05</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>1</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>1</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>1.05</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>1</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>1</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>1.05</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>1</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>1</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>1.05</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>1</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>1</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>1.05</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>1</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>1</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>1.05</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>3</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>1</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>1.05</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="6">
-        <v>2</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="7">
+        <v>2</v>
+      </c>
+      <c r="D15" s="7">
         <v>1</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>1.05</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="6">
-        <v>2</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="7">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7">
         <v>1</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>1.05</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="6">
-        <v>2</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="7">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7">
         <v>1</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="7">
         <v>1.05</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="F17" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>1</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="7">
         <v>1</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="7">
         <v>1.05</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="6">
-        <v>2</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="7">
+        <v>2</v>
+      </c>
+      <c r="D19" s="7">
         <v>1</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="7">
         <v>1.05</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="F19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>1</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="7">
         <v>1</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="7">
         <v>1.05</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <v>1</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="7">
         <v>1</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="7">
         <v>1.05</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="6">
-        <v>2</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="7">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7">
         <v>1</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="7">
         <v>1.05</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="7" t="s">
+      <c r="J22" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="6">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="7">
+        <v>2</v>
+      </c>
+      <c r="D23" s="7">
         <v>1</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="7">
         <v>1.05</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="F23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J23" s="7" t="s">
+      <c r="J23" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="6">
-        <v>2</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="7">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7">
         <v>1</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="7">
         <v>1.05</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J24" s="7" t="s">
+      <c r="J24" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="10">
         <v>1</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="10">
         <v>1</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <v>1.05</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="9" t="s">
+      <c r="F25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="11" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2539,881 +2496,881 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-    </row>
-    <row r="2" spans="1:38" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+      <c r="AI1" s="16"/>
+      <c r="AJ1" s="7"/>
+      <c r="AK1" s="7"/>
+      <c r="AL1" s="7"/>
+    </row>
+    <row r="2" spans="1:38" s="22" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="18" t="s">
+      <c r="N2" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="P2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="Q2" s="18" t="s">
+      <c r="Q2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="R2" s="19" t="s">
+      <c r="R2" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-      <c r="AB2" s="20"/>
-      <c r="AC2" s="20"/>
-      <c r="AD2" s="20"/>
-      <c r="AE2" s="20"/>
-      <c r="AF2" s="20"/>
-      <c r="AG2" s="20"/>
-      <c r="AH2" s="20"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="20"/>
-      <c r="AK2" s="20"/>
-      <c r="AL2" s="20"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="21"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="21"/>
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="21"/>
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="21"/>
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="21"/>
+      <c r="AL2" s="21"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
+      <c r="AH3" s="7"/>
+      <c r="AI3" s="7"/>
+      <c r="AJ3" s="7"/>
+      <c r="AK3" s="7"/>
+      <c r="AL3" s="7"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
+      <c r="AG4" s="7"/>
+      <c r="AH4" s="7"/>
+      <c r="AI4" s="7"/>
+      <c r="AJ4" s="7"/>
+      <c r="AK4" s="7"/>
+      <c r="AL4" s="7"/>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R5" s="7" t="s">
+      <c r="R5" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="6"/>
-      <c r="AL5" s="6"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="7"/>
+      <c r="AJ5" s="7"/>
+      <c r="AK5" s="7"/>
+      <c r="AL5" s="7"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R6" s="7" t="s">
+      <c r="R6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="7"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="7"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="Q7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R7" s="7" t="s">
+      <c r="R7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="6"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="6"/>
-      <c r="AK7" s="6"/>
-      <c r="AL7" s="6"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="7"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="Q8" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R8" s="7" t="s">
+      <c r="R8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="6"/>
-      <c r="AD8" s="6"/>
-      <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="6"/>
-      <c r="AK8" s="6"/>
-      <c r="AL8" s="6"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="7"/>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="Q9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="6"/>
-      <c r="AK9" s="6"/>
-      <c r="AL9" s="6"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="7"/>
+      <c r="AJ9" s="7"/>
+      <c r="AK9" s="7"/>
+      <c r="AL9" s="7"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="O10" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="Q10" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="6"/>
-      <c r="AJ10" s="6"/>
-      <c r="AK10" s="6"/>
-      <c r="AL10" s="6"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="7"/>
+      <c r="AJ10" s="7"/>
+      <c r="AK10" s="7"/>
+      <c r="AL10" s="7"/>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="O11" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="Q11" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="R11" s="7" t="s">
+      <c r="R11" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
-      <c r="AA11" s="6"/>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="7"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="9">
+        <v>10</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="Q12" s="9" t="s">
+      <c r="Q12" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="R12" s="10" t="s">
+      <c r="R12" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="6"/>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-      <c r="AJ12" s="6"/>
-      <c r="AK12" s="6"/>
-      <c r="AL12" s="6"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+      <c r="AA12" s="7"/>
+      <c r="AB12" s="7"/>
+      <c r="AC12" s="7"/>
+      <c r="AD12" s="7"/>
+      <c r="AE12" s="7"/>
+      <c r="AF12" s="7"/>
+      <c r="AG12" s="7"/>
+      <c r="AH12" s="7"/>
+      <c r="AI12" s="7"/>
+      <c r="AJ12" s="7"/>
+      <c r="AK12" s="7"/>
+      <c r="AL12" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3430,7 +3387,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1025" width="9.1640625" customWidth="1"/>
@@ -3444,14 +3401,6 @@
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3459,97 +3408,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{985F0CD3-3E83-B141-A42F-FDCB2F81F258}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:11" s="22" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>351</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>354</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>355</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>359</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="B2" s="23">
-        <v>3</v>
-      </c>
-      <c r="C2" s="23">
-        <v>0</v>
-      </c>
-      <c r="D2" s="23">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23">
-        <v>3000</v>
-      </c>
-      <c r="F2" s="23">
-        <v>250</v>
-      </c>
-      <c r="G2" s="23">
-        <v>250</v>
-      </c>
-      <c r="H2" s="23">
-        <v>87</v>
-      </c>
-      <c r="I2" s="23">
-        <v>87</v>
-      </c>
-      <c r="J2" s="23">
-        <v>0</v>
-      </c>
-      <c r="K2" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3562,362 +3420,362 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4">
+      <c r="E3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4">
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="4">
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="E12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="4">
+      <c r="E17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="5">
         <v>7000</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="4">
+      <c r="E18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="5">
         <v>7000</v>
       </c>
     </row>
@@ -3936,1396 +3794,1396 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="4">
         <v>0</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="7">
         <v>0</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="7">
         <v>0</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="7">
         <v>0</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <v>0</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="7">
         <v>0</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="7">
         <v>0</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="7">
         <v>0</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="7">
         <v>0</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="7">
         <v>0</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="7">
         <v>0</v>
       </c>
-      <c r="M12" s="7">
+      <c r="M12" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="7">
         <v>0</v>
       </c>
-      <c r="M13" s="7">
+      <c r="M13" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="7">
         <v>0</v>
       </c>
-      <c r="M14" s="4">
+      <c r="M14" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="7">
         <v>0</v>
       </c>
-      <c r="M15" s="7">
+      <c r="M15" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="7">
         <v>0</v>
       </c>
-      <c r="M16" s="7">
+      <c r="M16" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="7">
         <v>0</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M17" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="7">
         <v>0</v>
       </c>
-      <c r="M18" s="7">
+      <c r="M18" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="7">
         <v>0</v>
       </c>
-      <c r="M19" s="7">
+      <c r="M19" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="7">
         <v>0</v>
       </c>
-      <c r="M20" s="4">
+      <c r="M20" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="7">
         <v>0</v>
       </c>
-      <c r="M21" s="7">
+      <c r="M21" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="7">
         <v>0</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M22" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="7">
         <v>0</v>
       </c>
-      <c r="M23" s="4">
+      <c r="M23" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="7">
         <v>0</v>
       </c>
-      <c r="M24" s="7">
+      <c r="M24" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="7">
         <v>0</v>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="7">
         <v>0</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M26" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="7">
         <v>0</v>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="H28" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="7">
         <v>0</v>
       </c>
-      <c r="M28" s="7">
+      <c r="M28" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="H29" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="7">
         <v>0</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="7">
         <v>0</v>
       </c>
-      <c r="M30" s="7">
+      <c r="M30" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="7">
         <v>0</v>
       </c>
-      <c r="M31" s="7">
+      <c r="M31" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="7">
         <v>0</v>
       </c>
-      <c r="M32" s="4">
+      <c r="M32" s="5">
         <v>1E-3</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="H33" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="7">
         <v>0</v>
       </c>
-      <c r="M33" s="7">
+      <c r="M33" s="8">
         <v>1E-3</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="9" t="s">
+      <c r="D34" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I34" s="9" t="s">
+      <c r="I34" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="K34" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="L34" s="9">
+      <c r="L34" s="10">
         <v>0</v>
       </c>
-      <c r="M34" s="7">
+      <c r="M34" s="8">
         <v>1E-3</v>
       </c>
     </row>
@@ -5344,338 +5202,338 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="12" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="3">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="4">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="4">
         <v>0</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="13">
         <v>1E-3</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="7">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N3" s="6" t="s">
+      <c r="M3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="7">
         <v>0</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="13">
         <v>1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="6">
-        <v>2</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="7">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="6" t="s">
+      <c r="M4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="7">
         <v>0</v>
       </c>
-      <c r="R4" s="12">
+      <c r="R4" s="13">
         <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="7">
         <v>0</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="6" t="s">
+      <c r="M5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="7">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="7">
         <v>0</v>
       </c>
-      <c r="R5" s="12">
+      <c r="R5" s="13">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9">
-        <v>2</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>0</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="M6" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="9" t="s">
+      <c r="M6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="10">
         <v>1</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="10">
         <v>1.02</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="Q6" s="10">
         <v>0</v>
       </c>
-      <c r="R6" s="13">
+      <c r="R6" s="14">
         <v>1E-3</v>
       </c>
     </row>
@@ -5694,40 +5552,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>241</v>
       </c>
       <c r="M1" t="s">
@@ -5749,19 +5607,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -5797,19 +5655,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5828,73 +5686,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>261</v>
       </c>
       <c r="X1" t="s">
@@ -8493,7 +8351,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>347</v>
       </c>
     </row>
@@ -8758,13 +8616,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10F1EBA0-29BF-48E2-A80A-4674517565D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{283ECB0F-9DC4-463D-AB5C-7344926DA18D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC2D0AC-7F98-441E-A612-742C1D303422}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADF6D47C-DAB9-4556-83AC-1626B686AD2B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5205A12-A3DB-4C53-8C3E-4762946BF8BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83BA8154-7F3A-484B-A863-18DB2E8F099C}"/>
 </file>